--- a/resources/Z571/spc_sheet_oos_detail.xlsx
+++ b/resources/Z571/spc_sheet_oos_detail.xlsx
@@ -1236,7 +1236,7 @@
         <v>-4.028</v>
       </c>
       <c r="I9">
-        <v>0.4236938596491228</v>
+        <v>0.4236938596491229</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         <v>-3.8423</v>
       </c>
       <c r="I11">
-        <v>-0.07349649122807018</v>
+        <v>-0.0734964912280702</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1464,7 +1464,7 @@
         <v>-7.2497</v>
       </c>
       <c r="I15">
-        <v>-0.06564649122807018</v>
+        <v>-0.0656464912280702</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1540,7 +1540,7 @@
         <v>-7.6121</v>
       </c>
       <c r="I17">
-        <v>0.2972271929824561</v>
+        <v>0.2972271929824562</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -1578,7 +1578,7 @@
         <v>-6.2895</v>
       </c>
       <c r="I18">
-        <v>-0.5442815789473685</v>
+        <v>-0.5442815789473684</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>-6.7363</v>
       </c>
       <c r="I37">
-        <v>-0.07192368421052632</v>
+        <v>-0.07192368421052631</v>
       </c>
       <c r="J37">
         <v>6</v>
@@ -2490,7 +2490,7 @@
         <v>-8.690300000000001</v>
       </c>
       <c r="I42">
-        <v>0.6742280701754385</v>
+        <v>0.6742280701754386</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -2528,7 +2528,7 @@
         <v>-4.693</v>
       </c>
       <c r="I43">
-        <v>-0.01564473684210525</v>
+        <v>-0.01564473684210524</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -2642,7 +2642,7 @@
         <v>-4.7809</v>
       </c>
       <c r="I46">
-        <v>-0.09592719298245618</v>
+        <v>-0.09592719298245615</v>
       </c>
       <c r="J46">
         <v>6</v>
@@ -2832,7 +2832,7 @@
         <v>-7.0868</v>
       </c>
       <c r="I51">
-        <v>0.01521403508771931</v>
+        <v>0.0152140350877193</v>
       </c>
       <c r="J51">
         <v>6</v>
@@ -3022,7 +3022,7 @@
         <v>-5.3865</v>
       </c>
       <c r="I56">
-        <v>-0.07111140350877193</v>
+        <v>-0.07111140350877194</v>
       </c>
       <c r="J56">
         <v>6</v>
@@ -3250,7 +3250,7 @@
         <v>-3.8179</v>
       </c>
       <c r="I62">
-        <v>0.4341289473684211</v>
+        <v>0.434128947368421</v>
       </c>
       <c r="J62">
         <v>6</v>
@@ -4086,7 +4086,7 @@
         <v>-4.0084</v>
       </c>
       <c r="I84">
-        <v>0.0730719298245614</v>
+        <v>0.07307192982456141</v>
       </c>
       <c r="J84">
         <v>6</v>
@@ -4314,7 +4314,7 @@
         <v>-5.473</v>
       </c>
       <c r="I90">
-        <v>-0.4831271929824561</v>
+        <v>-0.4831271929824562</v>
       </c>
       <c r="J90">
         <v>6</v>
@@ -4922,7 +4922,7 @@
         <v>-5.5825</v>
       </c>
       <c r="I106">
-        <v>-0.7054438596491227</v>
+        <v>-0.7054438596491228</v>
       </c>
       <c r="J106">
         <v>6</v>
@@ -5188,7 +5188,7 @@
         <v>-4.0912</v>
       </c>
       <c r="I113">
-        <v>-0.4646464912280701</v>
+        <v>-0.4646464912280702</v>
       </c>
       <c r="J113">
         <v>6</v>
@@ -5264,7 +5264,7 @@
         <v>-4.786</v>
       </c>
       <c r="I115">
-        <v>0.7357850877192982</v>
+        <v>0.7357850877192983</v>
       </c>
       <c r="J115">
         <v>6</v>
@@ -5340,7 +5340,7 @@
         <v>-5.7432</v>
       </c>
       <c r="I117">
-        <v>-0.3705921052631579</v>
+        <v>-0.3705921052631578</v>
       </c>
       <c r="J117">
         <v>6</v>
@@ -5568,7 +5568,7 @@
         <v>-3.4283</v>
       </c>
       <c r="I123">
-        <v>0.9072131578947369</v>
+        <v>0.9072131578947368</v>
       </c>
       <c r="J123">
         <v>6</v>
@@ -5720,7 +5720,7 @@
         <v>-6.6898</v>
       </c>
       <c r="I127">
-        <v>-1.817302631578948</v>
+        <v>-1.817302631578947</v>
       </c>
       <c r="J127">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>-5.9035</v>
       </c>
       <c r="I141">
-        <v>0.02523508771929822</v>
+        <v>0.02523508771929824</v>
       </c>
       <c r="J141">
         <v>6</v>
@@ -6366,7 +6366,7 @@
         <v>-6.4897</v>
       </c>
       <c r="I144">
-        <v>0.2460368421052631</v>
+        <v>0.2460368421052632</v>
       </c>
       <c r="J144">
         <v>6</v>
@@ -6936,7 +6936,7 @@
         <v>-4.2829</v>
       </c>
       <c r="I159">
-        <v>-0.01571228070175439</v>
+        <v>-0.01571228070175438</v>
       </c>
       <c r="J159">
         <v>6</v>
@@ -7620,7 +7620,7 @@
         <v>-6.2438</v>
       </c>
       <c r="I177">
-        <v>-0.1918175438596491</v>
+        <v>-0.1918175438596492</v>
       </c>
       <c r="J177">
         <v>6</v>
@@ -8152,7 +8152,7 @@
         <v>-8.1807</v>
       </c>
       <c r="I191">
-        <v>-0.07521140350877192</v>
+        <v>-0.07521140350877191</v>
       </c>
       <c r="J191">
         <v>6</v>
@@ -9064,7 +9064,7 @@
         <v>-6.5139</v>
       </c>
       <c r="I215">
-        <v>-0.9538780701754386</v>
+        <v>-0.9538780701754387</v>
       </c>
       <c r="J215">
         <v>6</v>
@@ -9406,7 +9406,7 @@
         <v>-6.2778</v>
       </c>
       <c r="I224">
-        <v>-1.186399122807017</v>
+        <v>-1.186399122807018</v>
       </c>
       <c r="J224">
         <v>6</v>
@@ -9444,7 +9444,7 @@
         <v>-4.3643</v>
       </c>
       <c r="I225">
-        <v>0.005164035087719285</v>
+        <v>0.005164035087719296</v>
       </c>
       <c r="J225">
         <v>6</v>
@@ -9748,7 +9748,7 @@
         <v>-4.67</v>
       </c>
       <c r="I233">
-        <v>0.02424035087719301</v>
+        <v>0.024240350877193</v>
       </c>
       <c r="J233">
         <v>6</v>
@@ -10090,7 +10090,7 @@
         <v>-4.3593</v>
       </c>
       <c r="I242">
-        <v>0.09364473684210525</v>
+        <v>0.09364473684210524</v>
       </c>
       <c r="J242">
         <v>6</v>
@@ -11876,7 +11876,7 @@
         <v>-6.1702</v>
       </c>
       <c r="I289">
-        <v>-0.4964412280701755</v>
+        <v>-0.4964412280701754</v>
       </c>
       <c r="J289">
         <v>6</v>
@@ -12142,7 +12142,7 @@
         <v>-7.3934</v>
       </c>
       <c r="I296">
-        <v>-0.1600649122807018</v>
+        <v>-0.1600649122807017</v>
       </c>
       <c r="J296">
         <v>6</v>
@@ -12484,7 +12484,7 @@
         <v>-5.4199</v>
       </c>
       <c r="I305">
-        <v>0.1893789473684211</v>
+        <v>0.189378947368421</v>
       </c>
       <c r="J305">
         <v>6</v>
@@ -12864,7 +12864,7 @@
         <v>-4.338</v>
       </c>
       <c r="I315">
-        <v>-0.5713789473684211</v>
+        <v>-0.571378947368421</v>
       </c>
       <c r="J315">
         <v>6</v>
@@ -13472,7 +13472,7 @@
         <v>-4.215</v>
       </c>
       <c r="I331">
-        <v>-0.01164210526315792</v>
+        <v>-0.01164210526315791</v>
       </c>
       <c r="J331">
         <v>6</v>
@@ -14080,7 +14080,7 @@
         <v>-6.3326</v>
       </c>
       <c r="I347">
-        <v>0.05795438596491229</v>
+        <v>0.05795438596491228</v>
       </c>
       <c r="J347">
         <v>6</v>
@@ -14118,7 +14118,7 @@
         <v>-7.6893</v>
       </c>
       <c r="I348">
-        <v>-0.1874008771929824</v>
+        <v>-0.1874008771929825</v>
       </c>
       <c r="J348">
         <v>6</v>
@@ -15030,7 +15030,7 @@
         <v>-6.8786</v>
       </c>
       <c r="I372">
-        <v>0.006619298245614052</v>
+        <v>0.006619298245614042</v>
       </c>
       <c r="J372">
         <v>6</v>
